--- a/retail-ai-platform/docs/samples/SAMPLE_weekly_report_synthetic_2026-09.xlsx
+++ b/retail-ai-platform/docs/samples/SAMPLE_weekly_report_synthetic_2026-09.xlsx
@@ -10,14 +10,16 @@
     <sheet name="SKU" r:id="rId4" sheetId="2"/>
     <sheet name="Տվյալների որակ" r:id="rId5" sheetId="3"/>
     <sheet name="Աղբյուրներ" r:id="rId6" sheetId="4"/>
+    <sheet name="Համադրում" r:id="rId7" sheetId="5"/>
+    <sheet name="Առաջարկներ" r:id="rId8" sheetId="6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="89">
-  <si>
-    <t>Շաբաթական հաշվետվություն. Report Shop</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="150">
+  <si>
+    <t>Շաբաթական հաշվետվություն. Synthetic Sample</t>
   </si>
   <si>
     <t>Շրջան</t>
@@ -29,7 +31,7 @@
     <t>Պատրաստված</t>
   </si>
   <si>
-    <t>02.10.2026 18:00</t>
+    <t>12.10.2026 12:13</t>
   </si>
   <si>
     <t>Ցուցանիշ</t>
@@ -113,6 +115,33 @@
     <t>30</t>
   </si>
   <si>
+    <t>Բանկային մնացորդ (կանխիկ, ոչ շահույթ)</t>
+  </si>
+  <si>
+    <t>Գումար</t>
+  </si>
+  <si>
+    <t>Աղբյուր և ամսաթիվ</t>
+  </si>
+  <si>
+    <t>Main AMD account (AMD)</t>
+  </si>
+  <si>
+    <t>Վերջին հայտնի մնացորդ 02.09.2026 · աղբյուր՝ synthetic_bank_statement.csv, ներմուծված 12.10.2026 · հին է, թարմացնել քաղվածքը</t>
+  </si>
+  <si>
+    <t>acct ***0000 (AMD)</t>
+  </si>
+  <si>
+    <t>Վերջին հայտնի մնացորդ 02.09.2026 · աղբյուր՝ synthetic_statement.sta, ներմուծված 12.10.2026 · հին է, թարմացնել քաղվածքը</t>
+  </si>
+  <si>
+    <t>Ընդամենը բանկում (AMD)</t>
+  </si>
+  <si>
+    <t>02.09.2026 դրությամբ. սա շահույթ կամ ազատ ծախսելի գումար չէ</t>
+  </si>
+  <si>
     <t>Տվյալների վստահելիություն</t>
   </si>
   <si>
@@ -128,12 +157,6 @@
     <t>Պահեստի մնացորդ չի ներմուծվել. պաշարի օրերը հասանելի չեն</t>
   </si>
   <si>
-    <t>⚠ NO_MARKETING_DATA</t>
-  </si>
-  <si>
-    <t>Գովազդի ծախս չի ներմուծվել. ծածկույթը հաշվված է առանց մարքեթինգի</t>
-  </si>
-  <si>
     <t>⚠ VARIABLE_COSTS_ASSUMED</t>
   </si>
   <si>
@@ -236,6 +259,24 @@
     <t>Օրինակ</t>
   </si>
   <si>
+    <t>BANK</t>
+  </si>
+  <si>
+    <t>Սխալ (տողը չի ներմուծվել)</t>
+  </si>
+  <si>
+    <t>bad_number</t>
+  </si>
+  <si>
+    <t>Թիվը չի կարդացվում</t>
+  </si>
+  <si>
+    <t>debit</t>
+  </si>
+  <si>
+    <t>Cannot read number 'abc'</t>
+  </si>
+  <si>
     <t>HC_TRADE</t>
   </si>
   <si>
@@ -254,6 +295,21 @@
     <t>SKU 'A-1045' seen for the first time in HC_TRADE; check it is not an alias of an existing product</t>
   </si>
   <si>
+    <t>META_ADS</t>
+  </si>
+  <si>
+    <t>campaign_id_from_name</t>
+  </si>
+  <si>
+    <t>Արշավի ID չկա. օգտագործվել է անունը</t>
+  </si>
+  <si>
+    <t>campaign_id</t>
+  </si>
+  <si>
+    <t>No campaign id in file; name used as key</t>
+  </si>
+  <si>
     <t>Աղբյուրների վիճակ (վերջին ներմուծում)</t>
   </si>
   <si>
@@ -272,7 +328,7 @@
     <t>Սխալներ</t>
   </si>
   <si>
-    <t>02.10.2026 22:00</t>
+    <t>12.10.2026 16:13</t>
   </si>
   <si>
     <t>committed</t>
@@ -282,6 +338,135 @@
   </si>
   <si>
     <t>Բանկի մնացորդը ցուցադրվում է միայն աղբյուրի և ժամի հետ. հին տվյալը նշվում է «վերջին հայտնի մնացորդ»։</t>
+  </si>
+  <si>
+    <t>Բանկ ↔ վաճառք համադրում</t>
+  </si>
+  <si>
+    <t>Մեթոդ</t>
+  </si>
+  <si>
+    <t>Վճարման եղանակ չկա. մուտքը համեմատվում է օրվա ընդհանուր վաճառքի հետ (թույլ ապացույց, «հավանական»)</t>
+  </si>
+  <si>
+    <t>Ներքին փոխանցումներ (սեփական հաշիվների միջև)</t>
+  </si>
+  <si>
+    <t>1 հատ</t>
+  </si>
+  <si>
+    <t>Չեն հաշվվում որպես եկամուտ կամ ծախս</t>
+  </si>
+  <si>
+    <t>Ներքին փոխանցումների գումար</t>
+  </si>
+  <si>
+    <t>Էքվայրինգ՝ համադրված / հավանական / չհամադրված</t>
+  </si>
+  <si>
+    <t>0 / 2 / 0</t>
+  </si>
+  <si>
+    <t>Քարտային վաճառքի օրեր առանց մուտքի</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Ստուգել բանկի հետ կամ քաղվածքի ամբողջականությունը</t>
+  </si>
+  <si>
+    <t>Միջին հաշվարկային միջնորդավճար</t>
+  </si>
+  <si>
+    <t>Վաճառք − մուտք, հաշվարկային, ոչ բանկի սակագին</t>
+  </si>
+  <si>
+    <t>Տեսակ</t>
+  </si>
+  <si>
+    <t>Բանկի օր</t>
+  </si>
+  <si>
+    <t>Վաճառքի օր</t>
+  </si>
+  <si>
+    <t>Վաճառք</t>
+  </si>
+  <si>
+    <t>Մուտք/ելք</t>
+  </si>
+  <si>
+    <t>Տարբերություն</t>
+  </si>
+  <si>
+    <t>Ուշացում (օր)</t>
+  </si>
+  <si>
+    <t>INTERNAL_TRANSFER_PAIR</t>
+  </si>
+  <si>
+    <t>MATCHED</t>
+  </si>
+  <si>
+    <t>02.09.2026</t>
+  </si>
+  <si>
+    <t>acct ***0000 → Main AMD account</t>
+  </si>
+  <si>
+    <t>ACQUIRING_SETTLEMENT</t>
+  </si>
+  <si>
+    <t>PLAUSIBLE</t>
+  </si>
+  <si>
+    <t>01.09.2026</t>
+  </si>
+  <si>
+    <t>31.08.2026</t>
+  </si>
+  <si>
+    <t>No payment method in sales data: only checked settlement &lt;= day total sales</t>
+  </si>
+  <si>
+    <t>Քննարկելի առաջարկներ (որոշումը՝ մարդու)</t>
+  </si>
+  <si>
+    <t>Առաջարկները հաշվարկված են կանոններով. ոչ մի գնում, գովազդ կամ վճարում ավտոմատ չի կատարվում։</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Ապրանք</t>
+  </si>
+  <si>
+    <t>Վստահություն</t>
+  </si>
+  <si>
+    <t>Որոշում</t>
+  </si>
+  <si>
+    <t>f4452178-055f-43f3-9b92-c2b9ae708efb</t>
+  </si>
+  <si>
+    <t>ASK_ACCOUNTANT</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>PUBLISHABLE</t>
+  </si>
+  <si>
+    <t>Հարց հաշվապահին՝ հաստատել բանաձևերի հաստատումը հաշվապահի կողմից։ Մինչ այդ շահույթի թվերը նախնական են։ Շրջան՝ 01.09.2026 – 30.09.2026։ Վստահություն՝ բարձր։ Պատասխանատու՝ հաշվապահ։</t>
+  </si>
+  <si>
+    <t>template</t>
+  </si>
+  <si>
+    <t>ACCEPTED / REJECTED / NEED_DATA</t>
   </si>
 </sst>
 </file>
@@ -384,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.0" customWidth="true"/>
@@ -429,7 +614,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="n" s="6">
-        <v>6621600.0</v>
+        <v>5595000.0</v>
       </c>
       <c r="C6" t="s" s="5">
         <v>9</v>
@@ -462,7 +647,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="n" s="6">
-        <v>5380916.67</v>
+        <v>4525416.67</v>
       </c>
       <c r="C9" t="s" s="5">
         <v>15</v>
@@ -484,7 +669,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="n" s="6">
-        <v>2015116.67</v>
+        <v>1159616.67</v>
       </c>
       <c r="C11" t="s" s="5">
         <v>19</v>
@@ -506,7 +691,7 @@
         <v>22</v>
       </c>
       <c r="B13" t="n" s="6">
-        <v>0.0</v>
+        <v>33600.0</v>
       </c>
       <c r="C13" t="s" s="5">
         <v>23</v>
@@ -528,7 +713,7 @@
         <v>26</v>
       </c>
       <c r="B15" t="n" s="6">
-        <v>2015116.67</v>
+        <v>1126016.67</v>
       </c>
       <c r="C15" t="s" s="5">
         <v>27</v>
@@ -561,50 +746,86 @@
         <v>32</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="3">
-        <v>33</v>
-      </c>
-      <c r="B20" t="s" s="4">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="B20" t="n" s="6">
+        <v>2598000.0</v>
+      </c>
+      <c r="C20" t="s" s="5">
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="3">
-        <v>35</v>
-      </c>
-      <c r="B21" t="s" s="4">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="B21" t="n" s="6">
+        <v>2148000.0</v>
+      </c>
+      <c r="C21" t="s" s="5">
+        <v>38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="3">
-        <v>37</v>
-      </c>
-      <c r="B22" t="s" s="4">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="3">
         <v>39</v>
       </c>
-      <c r="B23" t="s" s="4">
+      <c r="B22" t="n" s="6">
+        <v>4746000.0</v>
+      </c>
+      <c r="C22" t="s" s="5">
         <v>40</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s" s="4">
-        <v>42</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="3">
+        <v>44</v>
+      </c>
+      <c r="B26" t="s" s="4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="3">
+        <v>46</v>
+      </c>
+      <c r="B27" t="s" s="4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="B29" t="s" s="4">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -633,48 +854,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B1" t="s" s="2">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C1" t="s" s="2">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D1" t="s" s="2">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E1" t="s" s="2">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F1" t="s" s="2">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G1" t="s" s="2">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H1" t="s" s="2">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I1" t="s" s="2">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="J1" t="s" s="2">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K1" t="s" s="2">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="L1" t="s" s="2">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C2" t="n" s="7">
         <v>57.0</v>
@@ -683,36 +904,36 @@
         <v>0.0</v>
       </c>
       <c r="E2" t="n" s="6">
-        <v>1969333.33</v>
+        <v>1650833.33</v>
       </c>
       <c r="F2" t="n" s="6">
         <v>1254000.0</v>
       </c>
       <c r="G2" t="n" s="6">
-        <v>715333.33</v>
+        <v>396833.33</v>
       </c>
       <c r="H2" t="s" s="7">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I2" t="n" s="9">
         <v>1.9</v>
       </c>
       <c r="J2" t="s" s="10">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K2" t="s" s="4">
         <v>11</v>
       </c>
       <c r="L2" t="s" s="4">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="4">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s" s="4">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C3" t="n" s="7">
         <v>42.0</v>
@@ -721,36 +942,36 @@
         <v>1.0</v>
       </c>
       <c r="E3" t="n" s="6">
-        <v>1896800.0</v>
+        <v>1604000.0</v>
       </c>
       <c r="F3" t="n" s="6">
         <v>1189000.0</v>
       </c>
       <c r="G3" t="n" s="6">
-        <v>707800.0</v>
+        <v>415000.0</v>
       </c>
       <c r="H3" t="s" s="7">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I3" t="n" s="9">
         <v>1.367</v>
       </c>
       <c r="J3" t="s" s="10">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K3" t="s" s="4">
         <v>11</v>
       </c>
       <c r="L3" t="s" s="4">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C4" t="n" s="7">
         <v>33.0</v>
@@ -759,36 +980,36 @@
         <v>1.0</v>
       </c>
       <c r="E4" t="n" s="6">
-        <v>1106583.33</v>
+        <v>924583.33</v>
       </c>
       <c r="F4" t="n" s="6">
         <v>704000.0</v>
       </c>
       <c r="G4" t="n" s="6">
-        <v>402583.33</v>
+        <v>220583.33</v>
       </c>
       <c r="H4" t="s" s="7">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I4" t="n" s="9">
         <v>1.067</v>
       </c>
       <c r="J4" t="s" s="10">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K4" t="s" s="4">
         <v>11</v>
       </c>
       <c r="L4" t="s" s="4">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="4">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s" s="4">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C5" t="n" s="7">
         <v>23.0</v>
@@ -797,36 +1018,36 @@
         <v>0.0</v>
       </c>
       <c r="E5" t="n" s="6">
-        <v>260600.0</v>
+        <v>223000.0</v>
       </c>
       <c r="F5" t="n" s="6">
         <v>149500.0</v>
       </c>
       <c r="G5" t="n" s="6">
-        <v>111100.0</v>
+        <v>73500.0</v>
       </c>
       <c r="H5" t="s" s="7">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I5" t="n" s="9">
         <v>0.767</v>
       </c>
       <c r="J5" t="s" s="10">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K5" t="s" s="4">
         <v>11</v>
       </c>
       <c r="L5" t="s" s="4">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C6" t="n" s="7">
         <v>34.0</v>
@@ -835,28 +1056,28 @@
         <v>1.0</v>
       </c>
       <c r="E6" t="n" s="6">
-        <v>147600.0</v>
+        <v>123000.0</v>
       </c>
       <c r="F6" t="n" s="6">
         <v>69300.0</v>
       </c>
       <c r="G6" t="n" s="6">
-        <v>78300.0</v>
+        <v>53700.0</v>
       </c>
       <c r="H6" t="s" s="7">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I6" t="n" s="9">
         <v>1.1</v>
       </c>
       <c r="J6" t="s" s="10">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K6" t="s" s="4">
         <v>11</v>
       </c>
       <c r="L6" t="s" s="4">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.0" customWidth="true"/>
@@ -880,53 +1101,99 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="4">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s" s="4">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s" s="4">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s" s="4">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s" s="4">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F3" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="G3" t="s" s="4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="4">
+        <v>86</v>
+      </c>
+      <c r="B4" t="s" s="4">
+        <v>87</v>
+      </c>
+      <c r="C4" t="s" s="4">
+        <v>88</v>
+      </c>
+      <c r="D4" t="s" s="4">
+        <v>89</v>
+      </c>
+      <c r="E4" t="s" s="4">
+        <v>90</v>
+      </c>
+      <c r="F4" t="n" s="7">
         <v>5.0</v>
       </c>
-      <c r="G3" t="s" s="4">
-        <v>78</v>
+      <c r="G4" t="s" s="4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="4">
+        <v>92</v>
+      </c>
+      <c r="B5" t="s" s="4">
+        <v>87</v>
+      </c>
+      <c r="C5" t="s" s="4">
+        <v>93</v>
+      </c>
+      <c r="D5" t="s" s="4">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s" s="4">
+        <v>95</v>
+      </c>
+      <c r="F5" t="n" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="G5" t="s" s="4">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -936,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="18.0" customWidth="true"/>
@@ -950,55 +1217,385 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>84</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="4">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s" s="4">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C3" t="s" s="4">
+        <v>104</v>
+      </c>
+      <c r="D3" t="n" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="E3" t="n" s="7">
+        <v>7.0</v>
+      </c>
+      <c r="F3" t="n" s="7">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="4">
         <v>86</v>
       </c>
-      <c r="D3" t="n" s="7">
+      <c r="B4" t="s" s="4">
+        <v>103</v>
+      </c>
+      <c r="C4" t="s" s="4">
+        <v>104</v>
+      </c>
+      <c r="D4" t="n" s="7">
         <v>1.0</v>
       </c>
-      <c r="E3" t="n" s="7">
+      <c r="E4" t="n" s="7">
         <v>313.0</v>
       </c>
-      <c r="F3" t="n" s="7">
+      <c r="F4" t="n" s="7">
         <v>0.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="4">
+        <v>92</v>
+      </c>
+      <c r="B5" t="s" s="4">
+        <v>103</v>
+      </c>
+      <c r="C5" t="s" s="4">
+        <v>104</v>
+      </c>
+      <c r="D5" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E5" t="n" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="F5" t="n" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="3">
+        <v>105</v>
+      </c>
+      <c r="B7" t="s" s="4">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="46.0" customWidth="true"/>
+    <col min="2" max="2" width="14.0" customWidth="true"/>
+    <col min="3" max="3" width="12.0" customWidth="true"/>
+    <col min="4" max="4" width="12.0" customWidth="true"/>
+    <col min="5" max="5" width="14.0" customWidth="true"/>
+    <col min="6" max="6" width="14.0" customWidth="true"/>
+    <col min="7" max="7" width="14.0" customWidth="true"/>
+    <col min="8" max="8" width="12.0" customWidth="true"/>
+    <col min="9" max="9" width="60.0" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="3">
+        <v>108</v>
+      </c>
+      <c r="B2" t="s" s="4">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="3">
+        <v>110</v>
+      </c>
+      <c r="B3" t="s" s="4">
+        <v>111</v>
+      </c>
+      <c r="C3" t="s" s="5">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="3">
+        <v>113</v>
+      </c>
+      <c r="B4" t="n" s="6">
+        <v>300000.0</v>
+      </c>
+      <c r="C4" t="s" s="5">
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="3">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s" s="4">
-        <v>88</v>
+        <v>115</v>
+      </c>
+      <c r="C5" t="s" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="3">
+        <v>116</v>
+      </c>
+      <c r="B6" t="s" s="4">
+        <v>117</v>
+      </c>
+      <c r="C6" t="s" s="5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="3">
+        <v>119</v>
+      </c>
+      <c r="B7" t="s" s="8">
+        <v>64</v>
+      </c>
+      <c r="C7" t="s" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="4">
+        <v>128</v>
+      </c>
+      <c r="B10" t="s" s="4">
+        <v>129</v>
+      </c>
+      <c r="C10" t="s" s="4">
+        <v>130</v>
+      </c>
+      <c r="D10" t="s" s="4">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s" s="6">
+        <v>64</v>
+      </c>
+      <c r="F10" t="n" s="6">
+        <v>-300000.0</v>
+      </c>
+      <c r="G10" t="n" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="H10" t="n" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I10" t="s" s="4">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="4">
+        <v>132</v>
+      </c>
+      <c r="B11" t="s" s="4">
+        <v>133</v>
+      </c>
+      <c r="C11" t="s" s="4">
+        <v>134</v>
+      </c>
+      <c r="D11" t="s" s="4">
+        <v>135</v>
+      </c>
+      <c r="E11" t="n" s="6">
+        <v>263700.0</v>
+      </c>
+      <c r="F11" t="n" s="6">
+        <v>150000.0</v>
+      </c>
+      <c r="G11" t="n" s="6">
+        <v>113700.0</v>
+      </c>
+      <c r="H11" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="I11" t="s" s="4">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="4">
+        <v>132</v>
+      </c>
+      <c r="B12" t="s" s="4">
+        <v>133</v>
+      </c>
+      <c r="C12" t="s" s="4">
+        <v>134</v>
+      </c>
+      <c r="D12" t="s" s="4">
+        <v>134</v>
+      </c>
+      <c r="E12" t="n" s="6">
+        <v>280000.0</v>
+      </c>
+      <c r="F12" t="n" s="6">
+        <v>150000.0</v>
+      </c>
+      <c r="G12" t="n" s="6">
+        <v>130000.0</v>
+      </c>
+      <c r="H12" t="n" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I12" t="s" s="4">
+        <v>136</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="38.0" customWidth="true"/>
+    <col min="2" max="2" width="16.0" customWidth="true"/>
+    <col min="3" max="3" width="12.0" customWidth="true"/>
+    <col min="4" max="4" width="14.0" customWidth="true"/>
+    <col min="5" max="5" width="14.0" customWidth="true"/>
+    <col min="6" max="6" width="100.0" customWidth="true"/>
+    <col min="7" max="7" width="22.0" customWidth="true"/>
+    <col min="8" max="8" width="30.0" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="B2" t="s" s="4">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="5">
+        <v>143</v>
+      </c>
+      <c r="B5" t="s" s="4">
+        <v>144</v>
+      </c>
+      <c r="C5" t="s" s="4">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s" s="4">
+        <v>145</v>
+      </c>
+      <c r="E5" t="s" s="4">
+        <v>146</v>
+      </c>
+      <c r="F5" t="s" s="4">
+        <v>147</v>
+      </c>
+      <c r="G5" t="s" s="5">
+        <v>148</v>
+      </c>
+      <c r="H5" t="s" s="5">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/retail-ai-platform/docs/samples/SAMPLE_weekly_report_synthetic_2026-09.xlsx
+++ b/retail-ai-platform/docs/samples/SAMPLE_weekly_report_synthetic_2026-09.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="150">
-  <si>
-    <t>Շաբաթական հաշվետվություն. Synthetic Sample</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="158">
+  <si>
+    <t>Շաբաթական հաշվետվություն. Synthetic Sample 32073</t>
   </si>
   <si>
     <t>Շրջան</t>
@@ -31,7 +31,7 @@
     <t>Պատրաստված</t>
   </si>
   <si>
-    <t>12.10.2026 12:13</t>
+    <t>12.10.2026 17:02</t>
   </si>
   <si>
     <t>Ցուցանիշ</t>
@@ -82,7 +82,7 @@
     <t>COGS-ի ծածկույթ</t>
   </si>
   <si>
-    <t>Մաքուր վաճառքի մասը, որի ինքնարժեքը հայտնի է</t>
+    <t>Վաճառքի և վերադարձի շրջանառության մասը, որի ինքնարժեքը հայտնի է</t>
   </si>
   <si>
     <t>Գովազդի ծախս (ad spend)</t>
@@ -151,12 +151,6 @@
     <t>Բանաձևերը դեռ հաստատված չեն հաշվապահի կողմից (formula_v0)</t>
   </si>
   <si>
-    <t>⚠ NO_INVENTORY_SNAPSHOT</t>
-  </si>
-  <si>
-    <t>Պահեստի մնացորդ չի ներմուծվել. պաշարի օրերը հասանելի չեն</t>
-  </si>
-  <si>
     <t>⚠ VARIABLE_COSTS_ASSUMED</t>
   </si>
   <si>
@@ -190,7 +184,7 @@
     <t>Համախառն շահույթ</t>
   </si>
   <si>
-    <t>Մնացորդ</t>
+    <t>Մնացորդ (30.09.2026)</t>
   </si>
   <si>
     <t>Արագություն (հատ/օր)</t>
@@ -211,31 +205,43 @@
     <t>Վերնաշապիկ սպիտակ L</t>
   </si>
   <si>
+    <t>B-2001</t>
+  </si>
+  <si>
+    <t>Ջինս կլասիկ 32</t>
+  </si>
+  <si>
+    <t>A-1045</t>
+  </si>
+  <si>
+    <t>Վերնաշապիկ սպիտակ M</t>
+  </si>
+  <si>
+    <t>C-3010</t>
+  </si>
+  <si>
+    <t>Գոտի կաշվե</t>
+  </si>
+  <si>
+    <t>Այո</t>
+  </si>
+  <si>
+    <t>D-4100</t>
+  </si>
+  <si>
+    <t>Գուլպա 3 հատ</t>
+  </si>
+  <si>
+    <t>E-5001</t>
+  </si>
+  <si>
+    <t>Շարֆ բրդյա</t>
+  </si>
+  <si>
     <t>—</t>
   </si>
   <si>
-    <t>B-2001</t>
-  </si>
-  <si>
-    <t>Ջինս կլասիկ 32</t>
-  </si>
-  <si>
-    <t>A-1045</t>
-  </si>
-  <si>
-    <t>Վերնաշապիկ սպիտակ M</t>
-  </si>
-  <si>
-    <t>C-3010</t>
-  </si>
-  <si>
-    <t>Գոտի կաշվե</t>
-  </si>
-  <si>
-    <t>D-4100</t>
-  </si>
-  <si>
-    <t>Գուլպա 3 հատ</t>
+    <t>Ապրանքը կա միայն վաճառքում կամ միայն մնացորդում. հնարավոր է՝ կոդը փոխվել է</t>
   </si>
   <si>
     <t>Տվյալների որակ. ներմուծման նշումներ (վերջին 30 օր)</t>
@@ -298,16 +304,13 @@
     <t>META_ADS</t>
   </si>
   <si>
-    <t>campaign_id_from_name</t>
-  </si>
-  <si>
-    <t>Արշավի ID չկա. օգտագործվել է անունը</t>
-  </si>
-  <si>
-    <t>campaign_id</t>
-  </si>
-  <si>
-    <t>No campaign id in file; name used as key</t>
+    <t>mapped_column_missing</t>
+  </si>
+  <si>
+    <t>adset_name</t>
+  </si>
+  <si>
+    <t>Column 'Ad set name' (mapped to adset_name) is not in this file; the field is empty on every row</t>
   </si>
   <si>
     <t>Աղբյուրների վիճակ (վերջին ներմուծում)</t>
@@ -328,7 +331,7 @@
     <t>Սխալներ</t>
   </si>
   <si>
-    <t>12.10.2026 16:13</t>
+    <t>12.10.2026 17:01</t>
   </si>
   <si>
     <t>committed</t>
@@ -448,10 +451,10 @@
     <t>Որոշում</t>
   </si>
   <si>
-    <t>f4452178-055f-43f3-9b92-c2b9ae708efb</t>
-  </si>
-  <si>
-    <t>ASK_ACCOUNTANT</t>
+    <t>9f8b50f0-933a-4e98-880e-2f6b5785a041</t>
+  </si>
+  <si>
+    <t>RESTOCK</t>
   </si>
   <si>
     <t>HIGH</t>
@@ -460,13 +463,34 @@
     <t>PUBLISHABLE</t>
   </si>
   <si>
-    <t>Հարց հաշվապահին՝ հաստատել բանաձևերի հաստատումը հաշվապահի կողմից։ Մինչ այդ շահույթի թվերը նախնական են։ Շրջան՝ 01.09.2026 – 30.09.2026։ Վստահություն՝ բարձր։ Պատասխանատու՝ հաշվապահ։</t>
+    <t>Ապրանք A-1045 (Վերնաշապիկ սպիտակ M)․ մնացորդը 8 հատ է, վաճառքի արագությունը՝ 1.07 հատ/օր, պաշարը կբավարարի մոտ 7.5 օր։ Առաջարկ՝ ստուգել համալրման անհրաժեշտությունը։ Բացակայում է՝ մատակարարման ժամկետը։ Շրջան՝ 01.09.2026 – 30.09.2026։ Վստահություն՝ բարձր։ Պատասխանատու՝ պահեստ/գնումներ։</t>
   </si>
   <si>
     <t>template</t>
   </si>
   <si>
     <t>ACCEPTED / REJECTED / NEED_DATA</t>
+  </si>
+  <si>
+    <t>ac80abb8-0ded-45e4-8e7e-a20e2486a023</t>
+  </si>
+  <si>
+    <t>AD_TEST</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>Ապրանք B-2001 (Ջինս կլասիկ 32)․ մաքուր գինը մոտ 39 122 դրամ/հատ է, ինքնարժեքը՝ 29 000, պատվերի փոփոխական ծախսը՝ 0։ Մինչև գովազդը մնում է մոտ 10 122 դրամ/հատ։ Առաջարկ՝ սահմանափակ փորձարկում, որտեղ մեկ վաճառքի ձեռքբերման արժեքը չգերազանցի 10 122 դրամը։ Նշագրված պատվերները դեռ չեն ապացուցում հավելյալ վաճառք։ Ենթադրություն՝ պատվերի փոփոխական ծախսը։ Բացակայում է՝ հավելյալ վաճառքի ապացույց (հնարավոր է միայն փորձարկմամբ)։ Շրջան՝ 01.09.2026 – 30.09.2026։ Վստահություն՝ միջին։ Պատասխանատու՝ մարքեթոլոգ։</t>
+  </si>
+  <si>
+    <t>a8dde007-e4af-4133-9a30-ecb6241feac3</t>
+  </si>
+  <si>
+    <t>SLOW_MOVER</t>
+  </si>
+  <si>
+    <t>Ապրանք E-5001 (Շարֆ բրդյա)․ մնացորդը 25 հատ է, վաճառքի արագությունը՝ 0 հատ/օր։ Առաջարկ՝ վերանայել գինը կամ դադարեցնել համալրումը։ Բացակայում է՝ սեզոնայնության տվյալները, ապրանքի կոդի ստուգում (կոդը կարող է փոխված լինել)։ Շրջան՝ 01.09.2026 – 30.09.2026։ Վստահություն՝ միջին։ Պատասխանատու՝ սեփականատեր։</t>
   </si>
 </sst>
 </file>
@@ -569,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.0" customWidth="true"/>
@@ -812,20 +836,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="s" s="3">
+    <row r="28">
+      <c r="A28" t="s" s="3">
         <v>46</v>
       </c>
-      <c r="B27" t="s" s="4">
+      <c r="B28" t="s" s="4">
         <v>47</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="3">
-        <v>48</v>
-      </c>
-      <c r="B29" t="s" s="4">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +851,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -854,48 +870,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="B1" t="s" s="2">
+      <c r="D1" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="C1" t="s" s="2">
+      <c r="E1" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D1" t="s" s="2">
+      <c r="F1" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="E1" t="s" s="2">
+      <c r="G1" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="F1" t="s" s="2">
+      <c r="H1" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="G1" t="s" s="2">
+      <c r="I1" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="H1" t="s" s="2">
+      <c r="J1" t="s" s="2">
         <v>57</v>
       </c>
-      <c r="I1" t="s" s="2">
+      <c r="K1" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="J1" t="s" s="2">
+      <c r="L1" t="s" s="2">
         <v>59</v>
-      </c>
-      <c r="K1" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="L1" t="s" s="2">
-        <v>61</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C2" t="n" s="7">
         <v>57.0</v>
@@ -912,28 +928,28 @@
       <c r="G2" t="n" s="6">
         <v>396833.33</v>
       </c>
-      <c r="H2" t="s" s="7">
-        <v>64</v>
+      <c r="H2" t="n" s="7">
+        <v>60.0</v>
       </c>
       <c r="I2" t="n" s="9">
         <v>1.9</v>
       </c>
-      <c r="J2" t="s" s="10">
-        <v>64</v>
+      <c r="J2" t="n" s="10">
+        <v>31.6</v>
       </c>
       <c r="K2" t="s" s="4">
         <v>11</v>
       </c>
       <c r="L2" t="s" s="4">
-        <v>45</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="4">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s" s="4">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C3" t="n" s="7">
         <v>42.0</v>
@@ -950,28 +966,28 @@
       <c r="G3" t="n" s="6">
         <v>415000.0</v>
       </c>
-      <c r="H3" t="s" s="7">
-        <v>64</v>
+      <c r="H3" t="n" s="7">
+        <v>45.0</v>
       </c>
       <c r="I3" t="n" s="9">
         <v>1.367</v>
       </c>
-      <c r="J3" t="s" s="10">
-        <v>64</v>
+      <c r="J3" t="n" s="10">
+        <v>32.9</v>
       </c>
       <c r="K3" t="s" s="4">
         <v>11</v>
       </c>
       <c r="L3" t="s" s="4">
-        <v>45</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C4" t="n" s="7">
         <v>33.0</v>
@@ -988,28 +1004,28 @@
       <c r="G4" t="n" s="6">
         <v>220583.33</v>
       </c>
-      <c r="H4" t="s" s="7">
-        <v>64</v>
+      <c r="H4" t="n" s="7">
+        <v>8.0</v>
       </c>
       <c r="I4" t="n" s="9">
         <v>1.067</v>
       </c>
-      <c r="J4" t="s" s="10">
-        <v>64</v>
+      <c r="J4" t="n" s="10">
+        <v>7.5</v>
       </c>
       <c r="K4" t="s" s="4">
         <v>11</v>
       </c>
       <c r="L4" t="s" s="4">
-        <v>45</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="4">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s" s="4">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C5" t="n" s="7">
         <v>23.0</v>
@@ -1026,28 +1042,28 @@
       <c r="G5" t="n" s="6">
         <v>73500.0</v>
       </c>
-      <c r="H5" t="s" s="7">
-        <v>64</v>
+      <c r="H5" t="n" s="7">
+        <v>120.0</v>
       </c>
       <c r="I5" t="n" s="9">
         <v>0.767</v>
       </c>
-      <c r="J5" t="s" s="10">
-        <v>64</v>
+      <c r="J5" t="n" s="10">
+        <v>156.5</v>
       </c>
       <c r="K5" t="s" s="4">
+        <v>68</v>
+      </c>
+      <c r="L5" t="s" s="4">
         <v>11</v>
-      </c>
-      <c r="L5" t="s" s="4">
-        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C6" t="n" s="7">
         <v>34.0</v>
@@ -1064,20 +1080,58 @@
       <c r="G6" t="n" s="6">
         <v>53700.0</v>
       </c>
-      <c r="H6" t="s" s="7">
-        <v>64</v>
+      <c r="H6" t="n" s="7">
+        <v>70.0</v>
       </c>
       <c r="I6" t="n" s="9">
         <v>1.1</v>
       </c>
-      <c r="J6" t="s" s="10">
-        <v>64</v>
+      <c r="J6" t="n" s="10">
+        <v>63.6</v>
       </c>
       <c r="K6" t="s" s="4">
         <v>11</v>
       </c>
       <c r="L6" t="s" s="4">
-        <v>45</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="4">
+        <v>71</v>
+      </c>
+      <c r="B7" t="s" s="4">
+        <v>72</v>
+      </c>
+      <c r="C7" t="n" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="D7" t="n" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E7" t="n" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="F7" t="s" s="6">
+        <v>73</v>
+      </c>
+      <c r="G7" t="s" s="6">
+        <v>73</v>
+      </c>
+      <c r="H7" t="n" s="7">
+        <v>25.0</v>
+      </c>
+      <c r="I7" t="n" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="J7" t="s" s="10">
+        <v>73</v>
+      </c>
+      <c r="K7" t="s" s="4">
+        <v>68</v>
+      </c>
+      <c r="L7" t="s" s="4">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1101,99 +1155,99 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="4">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s" s="4">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s" s="4">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s" s="4">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s" s="4">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F3" t="n" s="7">
         <v>1.0</v>
       </c>
       <c r="G3" t="s" s="4">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s" s="4">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s" s="4">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s" s="4">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F4" t="n" s="7">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G4" t="s" s="4">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="4">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s" s="4">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s" s="4">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s" s="4">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s" s="4">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F5" t="n" s="7">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G5" t="s" s="4">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1217,38 +1271,38 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="4">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s" s="4">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s" s="4">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D3" t="n" s="7">
         <v>2.0</v>
@@ -1262,19 +1316,19 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s" s="4">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D4" t="n" s="7">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E4" t="n" s="7">
-        <v>313.0</v>
+        <v>324.0</v>
       </c>
       <c r="F4" t="n" s="7">
         <v>0.0</v>
@@ -1282,13 +1336,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="4">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s" s="4">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s" s="4">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D5" t="n" s="7">
         <v>1.0</v>
@@ -1302,10 +1356,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="3">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s" s="4">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1331,31 +1385,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="3">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="3">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B3" t="s" s="4">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C3" t="s" s="5">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="3">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" t="n" s="6">
         <v>300000.0</v>
@@ -1366,10 +1420,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="3">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B5" t="s" s="4">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s" s="5">
         <v>11</v>
@@ -1377,70 +1431,70 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="3">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C6" t="s" s="5">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="3">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="8">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s" s="5">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s" s="4">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D10" t="s" s="4">
         <v>11</v>
       </c>
       <c r="E10" t="s" s="6">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F10" t="n" s="6">
         <v>-300000.0</v>
@@ -1452,21 +1506,21 @@
         <v>0.0</v>
       </c>
       <c r="I10" t="s" s="4">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="4">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B11" t="s" s="4">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C11" t="s" s="4">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s" s="4">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E11" t="n" s="6">
         <v>263700.0</v>
@@ -1481,21 +1535,21 @@
         <v>1.0</v>
       </c>
       <c r="I11" t="s" s="4">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C12" t="s" s="4">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="s" s="4">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E12" t="n" s="6">
         <v>280000.0</v>
@@ -1510,7 +1564,7 @@
         <v>0.0</v>
       </c>
       <c r="I12" t="s" s="4">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1520,7 +1574,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.0" customWidth="true"/>
@@ -1535,67 +1589,119 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G4" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="G4" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="H4" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="5">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B5" t="s" s="4">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C5" t="s" s="4">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s" s="4">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E5" t="s" s="4">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F5" t="s" s="4">
+        <v>148</v>
+      </c>
+      <c r="G5" t="s" s="5">
+        <v>149</v>
+      </c>
+      <c r="H5" t="s" s="5">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="5">
+        <v>151</v>
+      </c>
+      <c r="B6" t="s" s="4">
+        <v>152</v>
+      </c>
+      <c r="C6" t="s" s="4">
+        <v>62</v>
+      </c>
+      <c r="D6" t="s" s="4">
+        <v>153</v>
+      </c>
+      <c r="E6" t="s" s="4">
         <v>147</v>
       </c>
-      <c r="G5" t="s" s="5">
-        <v>148</v>
-      </c>
-      <c r="H5" t="s" s="5">
+      <c r="F6" t="s" s="4">
+        <v>154</v>
+      </c>
+      <c r="G6" t="s" s="5">
         <v>149</v>
+      </c>
+      <c r="H6" t="s" s="5">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="5">
+        <v>155</v>
+      </c>
+      <c r="B7" t="s" s="4">
+        <v>156</v>
+      </c>
+      <c r="C7" t="s" s="4">
+        <v>71</v>
+      </c>
+      <c r="D7" t="s" s="4">
+        <v>153</v>
+      </c>
+      <c r="E7" t="s" s="4">
+        <v>147</v>
+      </c>
+      <c r="F7" t="s" s="4">
+        <v>157</v>
+      </c>
+      <c r="G7" t="s" s="5">
+        <v>149</v>
+      </c>
+      <c r="H7" t="s" s="5">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/retail-ai-platform/docs/samples/SAMPLE_weekly_report_synthetic_2026-09.xlsx
+++ b/retail-ai-platform/docs/samples/SAMPLE_weekly_report_synthetic_2026-09.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="158">
-  <si>
-    <t>Շաբաթական հաշվետվություն. Synthetic Sample 32073</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="157">
+  <si>
+    <t>Շաբաթական հաշվետվություն. Synthetic Sample 25036</t>
   </si>
   <si>
     <t>Շրջան</t>
@@ -31,7 +31,7 @@
     <t>Պատրաստված</t>
   </si>
   <si>
-    <t>12.10.2026 17:02</t>
+    <t>12.10.2026 17:11</t>
   </si>
   <si>
     <t>Ցուցանիշ</t>
@@ -46,7 +46,7 @@
     <t>Համախառն վաճառք (gross sales)</t>
   </si>
   <si>
-    <t>Վաճառքի տողերի գումար, զեղչից առաջ</t>
+    <t>Վաճառքի տողերի գումար, զեղչից առաջ, առանց ԱԱՀ, եթե ԱԱՀ-ի հիմքը հայտնի է</t>
   </si>
   <si>
     <t>Զեղչեր</t>
@@ -94,7 +94,7 @@
     <t>Փոփոխական ծախսեր (ենթադրություն)</t>
   </si>
   <si>
-    <t>Պատվերի ծախս × վաճառքի տողեր. հաստատել հաշվապահի հետ</t>
+    <t>Մեկ հատի ծախս × վաճառված հատեր. հաստատել հաշվապահի հետ</t>
   </si>
   <si>
     <t>Ծածկույթ (contribution)</t>
@@ -331,9 +331,6 @@
     <t>Սխալներ</t>
   </si>
   <si>
-    <t>12.10.2026 17:01</t>
-  </si>
-  <si>
     <t>committed</t>
   </si>
   <si>
@@ -451,7 +448,7 @@
     <t>Որոշում</t>
   </si>
   <si>
-    <t>9f8b50f0-933a-4e98-880e-2f6b5785a041</t>
+    <t>2aa617f2-81ef-439a-b9be-47c4298eb4df</t>
   </si>
   <si>
     <t>RESTOCK</t>
@@ -472,7 +469,7 @@
     <t>ACCEPTED / REJECTED / NEED_DATA</t>
   </si>
   <si>
-    <t>ac80abb8-0ded-45e4-8e7e-a20e2486a023</t>
+    <t>4f94798c-847a-46d0-ac5e-31b408038414</t>
   </si>
   <si>
     <t>AD_TEST</t>
@@ -481,10 +478,10 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>Ապրանք B-2001 (Ջինս կլասիկ 32)․ մաքուր գինը մոտ 39 122 դրամ/հատ է, ինքնարժեքը՝ 29 000, պատվերի փոփոխական ծախսը՝ 0։ Մինչև գովազդը մնում է մոտ 10 122 դրամ/հատ։ Առաջարկ՝ սահմանափակ փորձարկում, որտեղ մեկ վաճառքի ձեռքբերման արժեքը չգերազանցի 10 122 դրամը։ Նշագրված պատվերները դեռ չեն ապացուցում հավելյալ վաճառք։ Ենթադրություն՝ պատվերի փոփոխական ծախսը։ Բացակայում է՝ հավելյալ վաճառքի ապացույց (հնարավոր է միայն փորձարկմամբ)։ Շրջան՝ 01.09.2026 – 30.09.2026։ Վստահություն՝ միջին։ Պատասխանատու՝ մարքեթոլոգ։</t>
-  </si>
-  <si>
-    <t>a8dde007-e4af-4133-9a30-ecb6241feac3</t>
+    <t>Ապրանք B-2001 (Ջինս կլասիկ 32)․ մաքուր գինը մոտ 39 122 դրամ/հատ է, ինքնարժեքը՝ 29 000, մեկ հատի փոփոխական ծախսը՝ 0։ Մինչև գովազդը մնում է մոտ 10 122 դրամ/հատ։ Առաջարկ՝ սահմանափակ փորձարկում, որտեղ մեկ վաճառքի ձեռքբերման արժեքը չգերազանցի 10 122 դրամը։ Նշագրված պատվերները դեռ չեն ապացուցում հավելյալ վաճառք։ Ենթադրություն՝ մեկ հատի փոփոխական ծախսը (առաքում, միջնորդավճար, վերադարձ)։ Բացակայում է՝ հավելյալ վաճառքի ապացույց (հնարավոր է միայն փորձարկմամբ)։ Շրջան՝ 01.09.2026 – 30.09.2026։ Վստահություն՝ միջին։ Պատասխանատու՝ մարքեթոլոգ։</t>
+  </si>
+  <si>
+    <t>c5470a60-4f8a-4e9a-aeb1-f274daee1e6c</t>
   </si>
   <si>
     <t>SLOW_MOVER</t>
@@ -638,7 +635,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="n" s="6">
-        <v>5595000.0</v>
+        <v>4662500.0</v>
       </c>
       <c r="C6" t="s" s="5">
         <v>9</v>
@@ -649,7 +646,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="6">
-        <v>77000.0</v>
+        <v>64166.67</v>
       </c>
       <c r="C7" t="s" s="5">
         <v>11</v>
@@ -1299,10 +1296,10 @@
         <v>82</v>
       </c>
       <c r="B3" t="s" s="4">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s" s="4">
         <v>104</v>
-      </c>
-      <c r="C3" t="s" s="4">
-        <v>105</v>
       </c>
       <c r="D3" t="n" s="7">
         <v>2.0</v>
@@ -1319,10 +1316,10 @@
         <v>88</v>
       </c>
       <c r="B4" t="s" s="4">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s" s="4">
         <v>104</v>
-      </c>
-      <c r="C4" t="s" s="4">
-        <v>105</v>
       </c>
       <c r="D4" t="n" s="7">
         <v>2.0</v>
@@ -1339,10 +1336,10 @@
         <v>94</v>
       </c>
       <c r="B5" t="s" s="4">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s" s="4">
         <v>104</v>
-      </c>
-      <c r="C5" t="s" s="4">
-        <v>105</v>
       </c>
       <c r="D5" t="n" s="7">
         <v>1.0</v>
@@ -1356,10 +1353,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="3">
+        <v>105</v>
+      </c>
+      <c r="B7" t="s" s="4">
         <v>106</v>
-      </c>
-      <c r="B7" t="s" s="4">
-        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1385,31 +1382,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="3">
+        <v>108</v>
+      </c>
+      <c r="B2" t="s" s="4">
         <v>109</v>
-      </c>
-      <c r="B2" t="s" s="4">
-        <v>110</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="3">
+        <v>110</v>
+      </c>
+      <c r="B3" t="s" s="4">
         <v>111</v>
       </c>
-      <c r="B3" t="s" s="4">
+      <c r="C3" t="s" s="5">
         <v>112</v>
-      </c>
-      <c r="C3" t="s" s="5">
-        <v>113</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="3">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B4" t="n" s="6">
         <v>300000.0</v>
@@ -1420,10 +1417,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="3">
+        <v>114</v>
+      </c>
+      <c r="B5" t="s" s="4">
         <v>115</v>
-      </c>
-      <c r="B5" t="s" s="4">
-        <v>116</v>
       </c>
       <c r="C5" t="s" s="5">
         <v>11</v>
@@ -1431,64 +1428,64 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="3">
+        <v>116</v>
+      </c>
+      <c r="B6" t="s" s="4">
         <v>117</v>
       </c>
-      <c r="B6" t="s" s="4">
+      <c r="C6" t="s" s="5">
         <v>118</v>
-      </c>
-      <c r="C6" t="s" s="5">
-        <v>119</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="3">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="8">
         <v>73</v>
       </c>
       <c r="C7" t="s" s="5">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B9" t="s" s="2">
         <v>100</v>
       </c>
       <c r="C9" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="D9" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="D9" t="s" s="2">
+      <c r="E9" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="E9" t="s" s="2">
+      <c r="F9" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="F9" t="s" s="2">
+      <c r="G9" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="G9" t="s" s="2">
+      <c r="H9" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="H9" t="s" s="2">
-        <v>128</v>
-      </c>
       <c r="I9" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
+        <v>128</v>
+      </c>
+      <c r="B10" t="s" s="4">
         <v>129</v>
       </c>
-      <c r="B10" t="s" s="4">
+      <c r="C10" t="s" s="4">
         <v>130</v>
-      </c>
-      <c r="C10" t="s" s="4">
-        <v>131</v>
       </c>
       <c r="D10" t="s" s="4">
         <v>11</v>
@@ -1506,21 +1503,21 @@
         <v>0.0</v>
       </c>
       <c r="I10" t="s" s="4">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="4">
+        <v>132</v>
+      </c>
+      <c r="B11" t="s" s="4">
         <v>133</v>
       </c>
-      <c r="B11" t="s" s="4">
+      <c r="C11" t="s" s="4">
         <v>134</v>
       </c>
-      <c r="C11" t="s" s="4">
+      <c r="D11" t="s" s="4">
         <v>135</v>
-      </c>
-      <c r="D11" t="s" s="4">
-        <v>136</v>
       </c>
       <c r="E11" t="n" s="6">
         <v>263700.0</v>
@@ -1535,21 +1532,21 @@
         <v>1.0</v>
       </c>
       <c r="I11" t="s" s="4">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
+        <v>132</v>
+      </c>
+      <c r="B12" t="s" s="4">
         <v>133</v>
       </c>
-      <c r="B12" t="s" s="4">
+      <c r="C12" t="s" s="4">
         <v>134</v>
       </c>
-      <c r="C12" t="s" s="4">
-        <v>135</v>
-      </c>
       <c r="D12" t="s" s="4">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E12" t="n" s="6">
         <v>280000.0</v>
@@ -1564,7 +1561,7 @@
         <v>0.0</v>
       </c>
       <c r="I12" t="s" s="4">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1589,7 +1586,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2">
@@ -1597,21 +1594,21 @@
         <v>46</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C4" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="B4" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="C4" t="s" s="2">
+      <c r="D4" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="E4" t="s" s="2">
         <v>100</v>
@@ -1623,85 +1620,85 @@
         <v>76</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="5">
+        <v>143</v>
+      </c>
+      <c r="B5" t="s" s="4">
         <v>144</v>
-      </c>
-      <c r="B5" t="s" s="4">
-        <v>145</v>
       </c>
       <c r="C5" t="s" s="4">
         <v>64</v>
       </c>
       <c r="D5" t="s" s="4">
+        <v>145</v>
+      </c>
+      <c r="E5" t="s" s="4">
         <v>146</v>
       </c>
-      <c r="E5" t="s" s="4">
+      <c r="F5" t="s" s="4">
         <v>147</v>
       </c>
-      <c r="F5" t="s" s="4">
+      <c r="G5" t="s" s="5">
         <v>148</v>
       </c>
-      <c r="G5" t="s" s="5">
+      <c r="H5" t="s" s="5">
         <v>149</v>
-      </c>
-      <c r="H5" t="s" s="5">
-        <v>150</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="5">
+        <v>150</v>
+      </c>
+      <c r="B6" t="s" s="4">
         <v>151</v>
-      </c>
-      <c r="B6" t="s" s="4">
-        <v>152</v>
       </c>
       <c r="C6" t="s" s="4">
         <v>62</v>
       </c>
       <c r="D6" t="s" s="4">
+        <v>152</v>
+      </c>
+      <c r="E6" t="s" s="4">
+        <v>146</v>
+      </c>
+      <c r="F6" t="s" s="4">
         <v>153</v>
       </c>
-      <c r="E6" t="s" s="4">
-        <v>147</v>
-      </c>
-      <c r="F6" t="s" s="4">
-        <v>154</v>
-      </c>
       <c r="G6" t="s" s="5">
+        <v>148</v>
+      </c>
+      <c r="H6" t="s" s="5">
         <v>149</v>
-      </c>
-      <c r="H6" t="s" s="5">
-        <v>150</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="5">
+        <v>154</v>
+      </c>
+      <c r="B7" t="s" s="4">
         <v>155</v>
-      </c>
-      <c r="B7" t="s" s="4">
-        <v>156</v>
       </c>
       <c r="C7" t="s" s="4">
         <v>71</v>
       </c>
       <c r="D7" t="s" s="4">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E7" t="s" s="4">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F7" t="s" s="4">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G7" t="s" s="5">
+        <v>148</v>
+      </c>
+      <c r="H7" t="s" s="5">
         <v>149</v>
-      </c>
-      <c r="H7" t="s" s="5">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
